--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NORTH_CAROLINA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NORTH_CAROLINA_2017.xlsx
@@ -427,7 +427,7 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="5">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C178">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C316">
@@ -8203,7 +8203,7 @@
         <v>21</v>
       </c>
       <c r="D436">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="437">
@@ -11371,7 +11371,7 @@
         <v>21</v>
       </c>
       <c r="D612">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="613">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C723">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C840">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C841">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C890">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C891">
@@ -21523,7 +21523,7 @@
         <v>21</v>
       </c>
       <c r="D1176">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="1177">
@@ -22477,7 +22477,7 @@
         <v>21</v>
       </c>
       <c r="D1229">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="1230">
@@ -24637,7 +24637,7 @@
         <v>21</v>
       </c>
       <c r="D1349">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="1350">
@@ -24655,7 +24655,7 @@
         <v>21</v>
       </c>
       <c r="D1350">
-        <v>0.0009340390517279723</v>
+        <v>0.0009340390517279724</v>
       </c>
     </row>
     <row r="1351">
